--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958A3FAB-532D-433D-97AD-4A896F2A61C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA634C35-03C1-4634-A645-F27C02776D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA634C35-03C1-4634-A645-F27C02776D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7858EC3-5D91-471C-BBD0-2D4334FB4975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7858EC3-5D91-471C-BBD0-2D4334FB4975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0AD10A-C03B-4880-96F2-02B54A490734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0AD10A-C03B-4880-96F2-02B54A490734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B979126-BCE7-4F4F-AEFC-BAC5B162FCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B979126-BCE7-4F4F-AEFC-BAC5B162FCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA5667B-5881-48A3-BD00-EC09BBDE37BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA5667B-5881-48A3-BD00-EC09BBDE37BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C971BF-1A1A-406B-BD04-A6E5AD6D89A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C971BF-1A1A-406B-BD04-A6E5AD6D89A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490AFBA0-D46D-4FA4-814E-772BA527F6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490AFBA0-D46D-4FA4-814E-772BA527F6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB68C25-98A1-4C86-AE91-0036D451306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB68C25-98A1-4C86-AE91-0036D451306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76729949-D216-4991-911F-120B1F55CEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -100,6 +100,9 @@
     <t>Carolina</t>
   </si>
   <si>
+    <t>31/12/1899</t>
+  </si>
+  <si>
     <t>Colombie</t>
   </si>
   <si>
@@ -172,7 +175,7 @@
     <t>25/06/1990</t>
   </si>
   <si>
-    <t>RDC</t>
+    <t>République démocratique du Congo</t>
   </si>
   <si>
     <t>16/09/2025</t>
@@ -734,7 +737,7 @@
     <col min="2" max="2" width="13" style="7" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="7" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
@@ -851,16 +854,16 @@
         <v>24</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>22</v>
@@ -871,22 +874,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>22</v>
@@ -897,22 +900,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>22</v>
@@ -923,22 +926,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>22</v>
@@ -949,22 +952,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>22</v>
@@ -975,22 +978,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>22</v>
@@ -1001,22 +1004,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>22</v>
@@ -1027,22 +1030,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>22</v>
@@ -1053,22 +1056,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>22</v>
@@ -1079,13 +1082,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
@@ -1094,7 +1097,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>22</v>
@@ -1105,22 +1108,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1131,22 +1134,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>22</v>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76729949-D216-4991-911F-120B1F55CEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A0EE56-BF48-41BC-9038-055379484715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>Carolina</t>
-  </si>
-  <si>
-    <t>31/12/1899</t>
   </si>
   <si>
     <t>Colombie</t>
@@ -854,16 +851,16 @@
         <v>24</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>22</v>
@@ -874,22 +871,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>22</v>
@@ -900,22 +897,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>22</v>
@@ -926,22 +923,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="E9" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>22</v>
@@ -952,22 +949,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>22</v>
@@ -978,22 +975,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="E11" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>22</v>
@@ -1004,22 +1001,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>22</v>
@@ -1030,22 +1027,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="E13" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>22</v>
@@ -1056,22 +1053,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>22</v>
@@ -1082,13 +1079,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
@@ -1097,7 +1094,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>22</v>
@@ -1108,22 +1105,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1134,22 +1131,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="E17" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>22</v>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A0EE56-BF48-41BC-9038-055379484715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F149A128-6D80-4E6A-9AF1-24132645DC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="50">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Elizabeth</t>
   </si>
   <si>
-    <t>10/11/1973</t>
+    <t/>
   </si>
   <si>
     <t>Nigéria</t>
@@ -67,33 +67,18 @@
     <t>F</t>
   </si>
   <si>
-    <t>06/09/2022</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
     <t>BARSEGHIAN</t>
   </si>
   <si>
     <t>Norik</t>
   </si>
   <si>
-    <t>07/07/2006</t>
-  </si>
-  <si>
     <t>Arménie</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>CARBONO FERNANDEZ</t>
   </si>
   <si>
@@ -103,108 +88,63 @@
     <t>Colombie</t>
   </si>
   <si>
-    <t>16/01/2025</t>
-  </si>
-  <si>
     <t>CHEGGARI</t>
   </si>
   <si>
     <t>Nour Eddin</t>
   </si>
   <si>
-    <t>23/10/1994</t>
-  </si>
-  <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>31/05/2023</t>
-  </si>
-  <si>
     <t>HALILAJ</t>
   </si>
   <si>
     <t>Lindita</t>
   </si>
   <si>
-    <t>23/02/1979</t>
-  </si>
-  <si>
     <t>Albanie</t>
   </si>
   <si>
-    <t>09/11/2023</t>
-  </si>
-  <si>
     <t>KIAKU</t>
   </si>
   <si>
     <t>Ana Marcela</t>
   </si>
   <si>
-    <t>19/02/1992</t>
-  </si>
-  <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>20/09/2023</t>
-  </si>
-  <si>
     <t>LMABROUK</t>
   </si>
   <si>
     <t>Oussama</t>
   </si>
   <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
-    <t>01/02/2025</t>
-  </si>
-  <si>
     <t>MANGAY</t>
   </si>
   <si>
     <t>Paul</t>
   </si>
   <si>
-    <t>25/06/1990</t>
-  </si>
-  <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
     <t>MENAYAME NGOMA</t>
   </si>
   <si>
     <t>Mera</t>
   </si>
   <si>
-    <t>05/05/1994</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
     <t>MUSTAFAYEVA</t>
   </si>
   <si>
     <t>Gulkanim</t>
   </si>
   <si>
-    <t>17/09/1990</t>
-  </si>
-  <si>
     <t>Azerbaïdjan</t>
   </si>
   <si>
-    <t>26/06/2019</t>
-  </si>
-  <si>
     <t>NYINAWUMUNTU</t>
   </si>
   <si>
@@ -214,40 +154,22 @@
     <t>Rwanda</t>
   </si>
   <si>
-    <t>19/09/2024</t>
-  </si>
-  <si>
     <t>OYEKAN</t>
   </si>
   <si>
     <t>Patrick</t>
   </si>
   <si>
-    <t>17/01/1976</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
     <t>REYES OTERO</t>
   </si>
   <si>
     <t>Victor Hugo</t>
   </si>
   <si>
-    <t>29/05/1986</t>
-  </si>
-  <si>
-    <t>06/05/2025</t>
-  </si>
-  <si>
     <t>SAUCEDO  FERNANDEZ</t>
   </si>
   <si>
     <t>Verselia</t>
-  </si>
-  <si>
-    <t>03/07/1989</t>
   </si>
   <si>
     <t>Pérou</t>
@@ -808,10 +730,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -819,25 +741,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="F5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G5" s="13" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -845,25 +767,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -871,25 +793,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -897,25 +819,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -923,25 +845,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -949,25 +871,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -975,25 +897,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1001,25 +923,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1027,25 +949,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1053,25 +975,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1079,25 +1001,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1105,25 +1027,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1131,25 +1053,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F149A128-6D80-4E6A-9AF1-24132645DC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0853EEC-9FBD-460F-AF01-CC6A082D0368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0853EEC-9FBD-460F-AF01-CC6A082D0368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EDC22E-5154-4A22-985C-F14D880EE963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Elizabeth</t>
   </si>
   <si>
-    <t/>
+    <t>10/11/1973</t>
   </si>
   <si>
     <t>Nigéria</t>
@@ -67,18 +67,33 @@
     <t>F</t>
   </si>
   <si>
+    <t>06/09/2022</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
     <t>BARSEGHIAN</t>
   </si>
   <si>
     <t>Norik</t>
   </si>
   <si>
+    <t>07/07/2006</t>
+  </si>
+  <si>
     <t>Arménie</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>CARBONO FERNANDEZ</t>
   </si>
   <si>
@@ -88,63 +103,108 @@
     <t>Colombie</t>
   </si>
   <si>
+    <t>16/01/2025</t>
+  </si>
+  <si>
     <t>CHEGGARI</t>
   </si>
   <si>
     <t>Nour Eddin</t>
   </si>
   <si>
+    <t>23/10/1994</t>
+  </si>
+  <si>
     <t>Maroc</t>
   </si>
   <si>
+    <t>31/05/2023</t>
+  </si>
+  <si>
     <t>HALILAJ</t>
   </si>
   <si>
     <t>Lindita</t>
   </si>
   <si>
+    <t>23/02/1979</t>
+  </si>
+  <si>
     <t>Albanie</t>
   </si>
   <si>
+    <t>09/11/2023</t>
+  </si>
+  <si>
     <t>KIAKU</t>
   </si>
   <si>
     <t>Ana Marcela</t>
   </si>
   <si>
+    <t>19/02/1992</t>
+  </si>
+  <si>
     <t>Angola</t>
   </si>
   <si>
+    <t>20/09/2023</t>
+  </si>
+  <si>
     <t>LMABROUK</t>
   </si>
   <si>
     <t>Oussama</t>
   </si>
   <si>
+    <t>01/01/1994</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
     <t>MANGAY</t>
   </si>
   <si>
     <t>Paul</t>
   </si>
   <si>
+    <t>25/06/1990</t>
+  </si>
+  <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>MENAYAME NGOMA</t>
   </si>
   <si>
     <t>Mera</t>
   </si>
   <si>
+    <t>05/05/1994</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
     <t>MUSTAFAYEVA</t>
   </si>
   <si>
     <t>Gulkanim</t>
   </si>
   <si>
+    <t>17/09/1990</t>
+  </si>
+  <si>
     <t>Azerbaïdjan</t>
   </si>
   <si>
+    <t>26/06/2019</t>
+  </si>
+  <si>
     <t>NYINAWUMUNTU</t>
   </si>
   <si>
@@ -154,22 +214,40 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>19/09/2024</t>
+  </si>
+  <si>
     <t>OYEKAN</t>
   </si>
   <si>
     <t>Patrick</t>
   </si>
   <si>
+    <t>17/01/1976</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
     <t>REYES OTERO</t>
   </si>
   <si>
     <t>Victor Hugo</t>
   </si>
   <si>
+    <t>29/05/1986</t>
+  </si>
+  <si>
+    <t>06/05/2025</t>
+  </si>
+  <si>
     <t>SAUCEDO  FERNANDEZ</t>
   </si>
   <si>
     <t>Verselia</t>
+  </si>
+  <si>
+    <t>03/07/1989</t>
   </si>
   <si>
     <t>Pérou</t>
@@ -730,10 +808,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -741,25 +819,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -767,25 +845,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -793,25 +871,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -819,25 +897,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -845,25 +923,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -871,25 +949,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="F10" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -897,25 +975,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -923,25 +1001,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -949,25 +1027,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -975,25 +1053,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1001,25 +1079,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1027,25 +1105,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="G16" s="13" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1053,25 +1131,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
